--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_metropolitana.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>12.95612223002907</v>
+      </c>
+      <c r="C2">
         <v>14.69141671890712</v>
-      </c>
-      <c r="C2">
-        <v>12.95612223002907</v>
       </c>
       <c r="D2">
         <v>6.806695495289097</v>
       </c>
       <c r="E2">
-        <v>11.50936151208072</v>
+        <v>10.14991932998568</v>
       </c>
       <c r="F2">
         <v>78.34071915793359</v>
       </c>
       <c r="G2">
-        <v>10.14991932998568</v>
+        <v>11.50936151208072</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.25443145754316</v>
+      </c>
+      <c r="C3">
         <v>31.21758650050313</v>
-      </c>
-      <c r="C3">
-        <v>27.25443145754316</v>
       </c>
       <c r="D3">
         <v>3.203322588643689</v>
       </c>
       <c r="E3">
-        <v>19.69911590875788</v>
+        <v>17.19826112440776</v>
       </c>
       <c r="F3">
         <v>63.10262296683437</v>
       </c>
       <c r="G3">
-        <v>17.19826112440776</v>
+        <v>19.69911590875788</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.92580059332453</v>
+      </c>
+      <c r="C4">
         <v>30.98710703529492</v>
-      </c>
-      <c r="C4">
-        <v>25.92580059332453</v>
       </c>
       <c r="D4">
         <v>3.227148629463798</v>
       </c>
       <c r="E4">
-        <v>19.74796560945452</v>
+        <v>16.52241423929608</v>
       </c>
       <c r="F4">
         <v>63.72962015124939</v>
       </c>
       <c r="G4">
-        <v>16.52241423929608</v>
+        <v>19.74796560945452</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>25.57712101161594</v>
+      </c>
+      <c r="C5">
         <v>34.88089986766652</v>
-      </c>
-      <c r="C5">
-        <v>25.57712101161594</v>
       </c>
       <c r="D5">
         <v>2.866898514068922</v>
       </c>
       <c r="E5">
-        <v>21.7383336006048</v>
+        <v>15.94007010148679</v>
       </c>
       <c r="F5">
         <v>62.32159629790841</v>
       </c>
       <c r="G5">
-        <v>15.94007010148679</v>
+        <v>21.7383336006048</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.68299614115207</v>
+      </c>
+      <c r="C6">
         <v>34.13136036853493</v>
-      </c>
-      <c r="C6">
-        <v>27.68299614115207</v>
       </c>
       <c r="D6">
         <v>2.929856850715746</v>
       </c>
       <c r="E6">
-        <v>21.09291233778238</v>
+        <v>17.10787394781923</v>
       </c>
       <c r="F6">
         <v>61.79921371439839</v>
       </c>
       <c r="G6">
-        <v>17.10787394781923</v>
+        <v>21.09291233778238</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>22.65670022712634</v>
+      </c>
+      <c r="C7">
         <v>24.68473507576528</v>
-      </c>
-      <c r="C7">
-        <v>22.65670022712634</v>
       </c>
       <c r="D7">
         <v>4.051086620661242</v>
       </c>
       <c r="E7">
-        <v>16.75342379081659</v>
+        <v>15.37700523993857</v>
       </c>
       <c r="F7">
         <v>67.86957096924483</v>
       </c>
       <c r="G7">
-        <v>15.37700523993857</v>
+        <v>16.75342379081659</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.44091349779166</v>
+      </c>
+      <c r="C8">
         <v>24.28863821732507</v>
-      </c>
-      <c r="C8">
-        <v>29.44091349779166</v>
       </c>
       <c r="D8">
         <v>4.117151365393145</v>
       </c>
       <c r="E8">
-        <v>15.7995895690475</v>
+        <v>19.1511086640973</v>
       </c>
       <c r="F8">
         <v>65.04930176685521</v>
       </c>
       <c r="G8">
-        <v>19.1511086640973</v>
+        <v>15.7995895690475</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>23.57651356863138</v>
+      </c>
+      <c r="C9">
         <v>23.64282407697024</v>
-      </c>
-      <c r="C9">
-        <v>23.57651356863138</v>
       </c>
       <c r="D9">
         <v>4.229613166111023</v>
       </c>
       <c r="E9">
-        <v>16.05959139273209</v>
+        <v>16.01454941020498</v>
       </c>
       <c r="F9">
         <v>67.92585919706292</v>
       </c>
       <c r="G9">
-        <v>16.01454941020498</v>
+        <v>16.05959139273209</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.5139585287743</v>
+      </c>
+      <c r="C10">
         <v>33.66221330831689</v>
-      </c>
-      <c r="C10">
-        <v>24.5139585287743</v>
       </c>
       <c r="D10">
         <v>2.970689986546224</v>
       </c>
       <c r="E10">
-        <v>21.28146921079003</v>
+        <v>15.49788330572428</v>
       </c>
       <c r="F10">
         <v>63.22064748348569</v>
       </c>
       <c r="G10">
-        <v>15.49788330572428</v>
+        <v>21.28146921079003</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>24.88745897279556</v>
+      </c>
+      <c r="C11">
         <v>35.25766597909612</v>
-      </c>
-      <c r="C11">
-        <v>24.88745897279556</v>
       </c>
       <c r="D11">
         <v>2.836262617590423</v>
       </c>
       <c r="E11">
-        <v>22.01607197826826</v>
+        <v>15.54056608358941</v>
       </c>
       <c r="F11">
         <v>62.44336193814232</v>
       </c>
       <c r="G11">
-        <v>15.54056608358941</v>
+        <v>22.01607197826826</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>26.88668956867877</v>
+      </c>
+      <c r="C12">
         <v>36.52053001799444</v>
-      </c>
-      <c r="C12">
-        <v>26.88668956867877</v>
       </c>
       <c r="D12">
         <v>2.738185890257559</v>
       </c>
       <c r="E12">
-        <v>22.3493980929181</v>
+        <v>16.45379539330435</v>
       </c>
       <c r="F12">
         <v>61.19680651377754</v>
       </c>
       <c r="G12">
-        <v>16.45379539330435</v>
+        <v>22.3493980929181</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>30.35947303505354</v>
+      </c>
+      <c r="C13">
         <v>28.21979514863343</v>
-      </c>
-      <c r="C13">
-        <v>30.35947303505354</v>
       </c>
       <c r="D13">
         <v>3.543611832520428</v>
       </c>
       <c r="E13">
-        <v>17.79538742475821</v>
+        <v>19.14466713258336</v>
       </c>
       <c r="F13">
         <v>63.05994544265843</v>
       </c>
       <c r="G13">
-        <v>19.14466713258336</v>
+        <v>17.79538742475821</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>23.94626303592121</v>
+      </c>
+      <c r="C14">
         <v>39.30149188876014</v>
-      </c>
-      <c r="C14">
-        <v>23.94626303592121</v>
       </c>
       <c r="D14">
         <v>2.54443267148846</v>
       </c>
       <c r="E14">
-        <v>24.07475184384184</v>
+        <v>14.66866300670992</v>
       </c>
       <c r="F14">
-        <v>61.25658514944822</v>
+        <v>61.25658514944823</v>
       </c>
       <c r="G14">
-        <v>14.66866300670992</v>
+        <v>24.07475184384185</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>19.99225128303031</v>
+      </c>
+      <c r="C15">
         <v>38.71663278942581</v>
-      </c>
-      <c r="C15">
-        <v>19.99225128303031</v>
       </c>
       <c r="D15">
         <v>2.582869242371505</v>
       </c>
       <c r="E15">
-        <v>24.39474829383233</v>
+        <v>12.59680666263342</v>
       </c>
       <c r="F15">
-        <v>63.00844504353426</v>
+        <v>63.00844504353424</v>
       </c>
       <c r="G15">
-        <v>12.59680666263342</v>
+        <v>24.39474829383232</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>27.26065635609204</v>
+      </c>
+      <c r="C16">
         <v>23.66503206337231</v>
-      </c>
-      <c r="C16">
-        <v>27.26065635609204</v>
       </c>
       <c r="D16">
         <v>4.225643968375414</v>
       </c>
       <c r="E16">
+        <v>18.06230380101174</v>
+      </c>
+      <c r="F16">
+        <v>66.25777297902545</v>
+      </c>
+      <c r="G16">
         <v>15.67992321996281</v>
-      </c>
-      <c r="F16">
-        <v>66.25777297902546</v>
-      </c>
-      <c r="G16">
-        <v>18.06230380101174</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.57595645910037</v>
+      </c>
+      <c r="C17">
         <v>34.2948615335361</v>
-      </c>
-      <c r="C17">
-        <v>26.57595645910037</v>
       </c>
       <c r="D17">
         <v>2.915888722927558</v>
       </c>
       <c r="E17">
-        <v>21.31826142334023</v>
+        <v>16.52006049992039</v>
       </c>
       <c r="F17">
-        <v>62.16167807673936</v>
+        <v>62.16167807673938</v>
       </c>
       <c r="G17">
-        <v>16.52006049992039</v>
+        <v>21.31826142334024</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.07079139045749</v>
+      </c>
+      <c r="C18">
         <v>34.34814632948687</v>
-      </c>
-      <c r="C18">
-        <v>25.07079139045749</v>
       </c>
       <c r="D18">
         <v>2.911365260900643</v>
       </c>
       <c r="E18">
-        <v>21.54583816750003</v>
+        <v>15.72635707465323</v>
       </c>
       <c r="F18">
         <v>62.72780475784675</v>
       </c>
       <c r="G18">
-        <v>15.72635707465323</v>
+        <v>21.54583816750003</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>22.78040319742597</v>
+      </c>
+      <c r="C19">
         <v>35.11889799406767</v>
-      </c>
-      <c r="C19">
-        <v>22.78040319742597</v>
       </c>
       <c r="D19">
         <v>2.847469758786057</v>
       </c>
       <c r="E19">
-        <v>22.24132578742508</v>
+        <v>14.42717163757353</v>
       </c>
       <c r="F19">
         <v>63.33150257500139</v>
       </c>
       <c r="G19">
-        <v>14.42717163757353</v>
+        <v>22.24132578742508</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>25.52754268012355</v>
+      </c>
+      <c r="C20">
         <v>30.32764882118625</v>
-      </c>
-      <c r="C20">
-        <v>25.52754268012355</v>
       </c>
       <c r="D20">
         <v>3.297321219643711</v>
       </c>
       <c r="E20">
+        <v>16.37901338686496</v>
+      </c>
+      <c r="F20">
+        <v>64.16212320983841</v>
+      </c>
+      <c r="G20">
         <v>19.45886340329663</v>
-      </c>
-      <c r="F20">
-        <v>64.16212320983843</v>
-      </c>
-      <c r="G20">
-        <v>16.37901338686496</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>19.61275642323182</v>
+      </c>
+      <c r="C21">
         <v>33.23677836796516</v>
-      </c>
-      <c r="C21">
-        <v>19.61275642323182</v>
       </c>
       <c r="D21">
         <v>3.008715191734218</v>
       </c>
       <c r="E21">
-        <v>21.74476907199547</v>
+        <v>12.83141388033938</v>
       </c>
       <c r="F21">
         <v>65.42381704766515</v>
       </c>
       <c r="G21">
-        <v>12.83141388033938</v>
+        <v>21.74476907199547</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>25.70325515827246</v>
+      </c>
+      <c r="C22">
         <v>41.32705369729591</v>
-      </c>
-      <c r="C22">
-        <v>25.70325515827246</v>
       </c>
       <c r="D22">
         <v>2.419722459105357</v>
       </c>
       <c r="E22">
+        <v>15.38837791439286</v>
+      </c>
+      <c r="F22">
+        <v>59.86937381913741</v>
+      </c>
+      <c r="G22">
         <v>24.74224826646973</v>
-      </c>
-      <c r="F22">
-        <v>59.8693738191374</v>
-      </c>
-      <c r="G22">
-        <v>15.38837791439285</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>24.99376243514532</v>
+      </c>
+      <c r="C23">
         <v>28.14965037649302</v>
-      </c>
-      <c r="C23">
-        <v>24.99376243514532</v>
       </c>
       <c r="D23">
         <v>3.552441989954774</v>
       </c>
       <c r="E23">
-        <v>18.38123485671317</v>
+        <v>16.32049461107862</v>
       </c>
       <c r="F23">
         <v>65.29827053220821</v>
       </c>
       <c r="G23">
-        <v>16.32049461107862</v>
+        <v>18.38123485671317</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>15.35214233077166</v>
+      </c>
+      <c r="C24">
         <v>34.22254974207812</v>
-      </c>
-      <c r="C24">
-        <v>15.35214233077166</v>
       </c>
       <c r="D24">
         <v>2.922049956933678</v>
       </c>
       <c r="E24">
-        <v>22.87990653218938</v>
+        <v>10.26386357078005</v>
       </c>
       <c r="F24">
-        <v>66.85622989703056</v>
+        <v>66.85622989703057</v>
       </c>
       <c r="G24">
-        <v>10.26386357078005</v>
+        <v>22.87990653218939</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.16071664086741</v>
+      </c>
+      <c r="C25">
         <v>26.55055844399248</v>
-      </c>
-      <c r="C25">
-        <v>27.16071664086741</v>
       </c>
       <c r="D25">
         <v>3.766399121545661</v>
       </c>
       <c r="E25">
-        <v>17.27300643972579</v>
+        <v>17.66995727923843</v>
       </c>
       <c r="F25">
         <v>65.05703628103578</v>
       </c>
       <c r="G25">
-        <v>17.66995727923843</v>
+        <v>17.27300643972579</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.80105191266449</v>
+      </c>
+      <c r="C26">
         <v>18.34580748730875</v>
-      </c>
-      <c r="C26">
-        <v>27.80105191266449</v>
       </c>
       <c r="D26">
         <v>5.45083665950261</v>
       </c>
       <c r="E26">
-        <v>12.55299468126108</v>
+        <v>19.02268172357974</v>
       </c>
       <c r="F26">
         <v>68.42432359515918</v>
       </c>
       <c r="G26">
-        <v>19.02268172357974</v>
+        <v>12.55299468126108</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>23.30699973001209</v>
+      </c>
+      <c r="C27">
         <v>29.47094108394277</v>
-      </c>
-      <c r="C27">
-        <v>23.30699973001209</v>
       </c>
       <c r="D27">
         <v>3.393172946705967</v>
       </c>
       <c r="E27">
+        <v>15.25547445255474</v>
+      </c>
+      <c r="F27">
+        <v>65.45447560507107</v>
+      </c>
+      <c r="G27">
         <v>19.29004994237419</v>
-      </c>
-      <c r="F27">
-        <v>65.45447560507108</v>
-      </c>
-      <c r="G27">
-        <v>15.25547445255475</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>24.80243548960451</v>
+      </c>
+      <c r="C28">
         <v>30.5028666223077</v>
-      </c>
-      <c r="C28">
-        <v>24.80243548960451</v>
       </c>
       <c r="D28">
         <v>3.278380397430151</v>
       </c>
       <c r="E28">
-        <v>19.64058290832047</v>
+        <v>15.97011509094004</v>
       </c>
       <c r="F28">
         <v>64.38930200073949</v>
       </c>
       <c r="G28">
-        <v>15.97011509094004</v>
+        <v>19.64058290832047</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.946360560863</v>
+      </c>
+      <c r="C29">
         <v>28.26230345326496</v>
-      </c>
-      <c r="C29">
-        <v>28.946360560863</v>
       </c>
       <c r="D29">
         <v>3.538282014605135</v>
       </c>
       <c r="E29">
-        <v>17.97757371102975</v>
+        <v>18.41270056099558</v>
       </c>
       <c r="F29">
         <v>63.60972572797466</v>
       </c>
       <c r="G29">
-        <v>18.41270056099558</v>
+        <v>17.97757371102975</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>24.18370894838322</v>
+      </c>
+      <c r="C30">
         <v>36.72440496886557</v>
-      </c>
-      <c r="C30">
-        <v>24.18370894838322</v>
       </c>
       <c r="D30">
         <v>2.722984894779877</v>
       </c>
       <c r="E30">
-        <v>22.82321511005471</v>
+        <v>15.02951489495448</v>
       </c>
       <c r="F30">
         <v>62.14726999499082</v>
       </c>
       <c r="G30">
-        <v>15.02951489495448</v>
+        <v>22.82321511005471</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>22.35133433635306</v>
+      </c>
+      <c r="C31">
         <v>25.82242282616815</v>
-      </c>
-      <c r="C31">
-        <v>22.35133433635306</v>
       </c>
       <c r="D31">
         <v>3.872603305785124</v>
       </c>
       <c r="E31">
-        <v>17.42712294043092</v>
+        <v>15.0845431501325</v>
       </c>
       <c r="F31">
         <v>67.48833390943656</v>
       </c>
       <c r="G31">
-        <v>15.0845431501325</v>
+        <v>17.42712294043092</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>25.41924095322153</v>
+      </c>
+      <c r="C32">
         <v>34.83929096793175</v>
-      </c>
-      <c r="C32">
-        <v>25.41924095322153</v>
       </c>
       <c r="D32">
         <v>2.870322478492637</v>
       </c>
       <c r="E32">
-        <v>21.739429751592</v>
+        <v>15.8613963628019</v>
       </c>
       <c r="F32">
-        <v>62.39917388560611</v>
+        <v>62.3991738856061</v>
       </c>
       <c r="G32">
-        <v>15.86139636280191</v>
+        <v>21.73942975159199</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>22.89289581077705</v>
+      </c>
+      <c r="C33">
         <v>41.20304822187057</v>
-      </c>
-      <c r="C33">
-        <v>22.89289581077705</v>
       </c>
       <c r="D33">
         <v>2.427004901713073</v>
       </c>
       <c r="E33">
-        <v>25.1091204385119</v>
+        <v>13.95092117951581</v>
       </c>
       <c r="F33">
         <v>60.93995838197229</v>
       </c>
       <c r="G33">
-        <v>13.95092117951581</v>
+        <v>25.1091204385119</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>27.58496727542158</v>
+      </c>
+      <c r="C34">
         <v>26.3618775812626</v>
-      </c>
-      <c r="C34">
-        <v>27.58496727542158</v>
       </c>
       <c r="D34">
         <v>3.793356512325117</v>
       </c>
       <c r="E34">
-        <v>17.1240129057559</v>
+        <v>17.91850122105564</v>
       </c>
       <c r="F34">
         <v>64.95748587318847</v>
       </c>
       <c r="G34">
-        <v>17.91850122105564</v>
+        <v>17.1240129057559</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>26.46740530791033</v>
+      </c>
+      <c r="C35">
         <v>30.17778922958</v>
-      </c>
-      <c r="C35">
-        <v>26.46740530791033</v>
       </c>
       <c r="D35">
         <v>3.313695355191257</v>
       </c>
       <c r="E35">
-        <v>19.26505905188012</v>
+        <v>16.89640425041945</v>
       </c>
       <c r="F35">
         <v>63.83853669770043</v>
       </c>
       <c r="G35">
-        <v>16.89640425041945</v>
+        <v>19.26505905188012</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>25.93290276282741</v>
+      </c>
+      <c r="C36">
         <v>33.93433799784714</v>
-      </c>
-      <c r="C36">
-        <v>25.93290276282741</v>
       </c>
       <c r="D36">
         <v>2.946867565424267</v>
       </c>
       <c r="E36">
-        <v>21.22657389743014</v>
+        <v>16.22152395915161</v>
       </c>
       <c r="F36">
         <v>62.55190214341825</v>
       </c>
       <c r="G36">
-        <v>16.22152395915161</v>
+        <v>21.22657389743014</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>34.14358338003363</v>
+      </c>
+      <c r="C37">
         <v>17.78980866223681</v>
-      </c>
-      <c r="C37">
-        <v>34.14358338003363</v>
       </c>
       <c r="D37">
         <v>5.62119592732182</v>
       </c>
       <c r="E37">
-        <v>11.70895247128254</v>
+        <v>22.4727315839393</v>
       </c>
       <c r="F37">
         <v>65.81831594477816</v>
       </c>
       <c r="G37">
-        <v>22.4727315839393</v>
+        <v>11.70895247128254</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>35.02671252429956</v>
+      </c>
+      <c r="C38">
         <v>16.50874784192711</v>
-      </c>
-      <c r="C38">
-        <v>35.02671252429956</v>
       </c>
       <c r="D38">
         <v>6.057394598155468</v>
       </c>
       <c r="E38">
-        <v>10.89431331915924</v>
+        <v>23.11453203075239</v>
       </c>
       <c r="F38">
         <v>65.99115465008836</v>
       </c>
       <c r="G38">
-        <v>23.11453203075239</v>
+        <v>10.89431331915924</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>32.13515456506111</v>
+      </c>
+      <c r="C39">
         <v>16.21854780733285</v>
-      </c>
-      <c r="C39">
-        <v>32.13515456506111</v>
       </c>
       <c r="D39">
         <v>6.165780141843972</v>
       </c>
       <c r="E39">
-        <v>10.93235123085869</v>
+        <v>21.66117464624927</v>
       </c>
       <c r="F39">
         <v>67.40647412289204</v>
       </c>
       <c r="G39">
-        <v>21.66117464624927</v>
+        <v>10.93235123085869</v>
       </c>
     </row>
     <row r="40">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B40">
+        <v>29.08173582988079</v>
+      </c>
+      <c r="C40">
         <v>25.84714782762</v>
-      </c>
-      <c r="C40">
-        <v>29.08173582988079</v>
       </c>
       <c r="D40">
         <v>3.868898830421089</v>
       </c>
       <c r="E40">
-        <v>16.68323376340847</v>
+        <v>18.77102264169888</v>
       </c>
       <c r="F40">
         <v>64.54574359489264</v>
       </c>
       <c r="G40">
-        <v>18.77102264169888</v>
+        <v>16.68323376340847</v>
       </c>
     </row>
     <row r="41">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B41">
+        <v>31.10513892443762</v>
+      </c>
+      <c r="C41">
         <v>23.70958109376333</v>
-      </c>
-      <c r="C41">
-        <v>31.10513892443762</v>
       </c>
       <c r="D41">
         <v>4.217704210147535</v>
       </c>
       <c r="E41">
-        <v>15.31481056257176</v>
+        <v>20.09184845005741</v>
       </c>
       <c r="F41">
         <v>64.59334098737084</v>
       </c>
       <c r="G41">
-        <v>20.09184845005741</v>
+        <v>15.31481056257176</v>
       </c>
     </row>
     <row r="42">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B42">
+        <v>22.8952772073922</v>
+      </c>
+      <c r="C42">
         <v>30.02835631172387</v>
-      </c>
-      <c r="C42">
-        <v>22.8952772073922</v>
       </c>
       <c r="D42">
         <v>3.330185607294041</v>
       </c>
       <c r="E42">
-        <v>19.63617762716199</v>
+        <v>14.97170625659388</v>
       </c>
       <c r="F42">
-        <v>65.39211611624411</v>
+        <v>65.39211611624413</v>
       </c>
       <c r="G42">
-        <v>14.97170625659388</v>
+        <v>19.636177627162</v>
       </c>
     </row>
     <row r="43">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B43">
+        <v>29.02061746892607</v>
+      </c>
+      <c r="C43">
         <v>27.40203009264144</v>
-      </c>
-      <c r="C43">
-        <v>29.02061746892607</v>
       </c>
       <c r="D43">
         <v>3.649364651520986</v>
       </c>
       <c r="E43">
-        <v>17.51794290648103</v>
+        <v>18.55269548324429</v>
       </c>
       <c r="F43">
         <v>63.92936161027468</v>
       </c>
       <c r="G43">
-        <v>18.55269548324429</v>
+        <v>17.51794290648103</v>
       </c>
     </row>
     <row r="44">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B44">
+        <v>29.55928790444373</v>
+      </c>
+      <c r="C44">
         <v>30.73085899958812</v>
-      </c>
-      <c r="C44">
-        <v>29.55928790444373</v>
       </c>
       <c r="D44">
         <v>3.254058078927774</v>
       </c>
       <c r="E44">
-        <v>19.17201998572448</v>
+        <v>18.44111349036402</v>
       </c>
       <c r="F44">
         <v>62.38686652391149</v>
       </c>
       <c r="G44">
-        <v>18.44111349036402</v>
+        <v>19.17201998572448</v>
       </c>
     </row>
     <row r="45">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B45">
+        <v>31.96086424785977</v>
+      </c>
+      <c r="C45">
         <v>29.94292702812882</v>
-      </c>
-      <c r="C45">
-        <v>31.96086424785977</v>
       </c>
       <c r="D45">
         <v>3.339686861810756</v>
       </c>
       <c r="E45">
-        <v>18.49427168576105</v>
+        <v>19.74065214654413</v>
       </c>
       <c r="F45">
         <v>61.76507616769482</v>
       </c>
       <c r="G45">
-        <v>19.74065214654413</v>
+        <v>18.49427168576105</v>
       </c>
     </row>
     <row r="46">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B46">
+        <v>28.60846217942783</v>
+      </c>
+      <c r="C46">
         <v>32.86269789834274</v>
-      </c>
-      <c r="C46">
-        <v>28.60846217942783</v>
       </c>
       <c r="D46">
         <v>3.042963797717988</v>
       </c>
       <c r="E46">
-        <v>20.35205412688857</v>
+        <v>17.71738195579255</v>
       </c>
       <c r="F46">
         <v>61.93056391731889</v>
       </c>
       <c r="G46">
-        <v>17.71738195579255</v>
+        <v>20.35205412688857</v>
       </c>
     </row>
     <row r="47">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B47">
+        <v>29.99675710733974</v>
+      </c>
+      <c r="C47">
         <v>34.32061398767701</v>
-      </c>
-      <c r="C47">
-        <v>29.99675710733974</v>
       </c>
       <c r="D47">
         <v>2.913700787401575</v>
       </c>
       <c r="E47">
-        <v>20.88678376422604</v>
+        <v>18.25537793566213</v>
       </c>
       <c r="F47">
         <v>60.85783830011184</v>
       </c>
       <c r="G47">
-        <v>18.25537793566213</v>
+        <v>20.88678376422604</v>
       </c>
     </row>
     <row r="48">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B48">
+        <v>31.45811426568524</v>
+      </c>
+      <c r="C48">
         <v>39.2043463021381</v>
-      </c>
-      <c r="C48">
-        <v>31.45811426568524</v>
       </c>
       <c r="D48">
         <v>2.550737594993294</v>
       </c>
       <c r="E48">
-        <v>22.97186280550421</v>
+        <v>18.43294310946806</v>
       </c>
       <c r="F48">
         <v>58.59519408502772</v>
       </c>
       <c r="G48">
-        <v>18.43294310946806</v>
+        <v>22.97186280550421</v>
       </c>
     </row>
     <row r="49">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B49">
+        <v>27.68688910655857</v>
+      </c>
+      <c r="C49">
         <v>28.76018589917263</v>
-      </c>
-      <c r="C49">
-        <v>27.68688910655857</v>
       </c>
       <c r="D49">
         <v>3.477028985507246</v>
       </c>
       <c r="E49">
-        <v>18.38333244524964</v>
+        <v>17.69728779240155</v>
       </c>
       <c r="F49">
         <v>63.9193797623488</v>
       </c>
       <c r="G49">
-        <v>17.69728779240155</v>
+        <v>18.38333244524964</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B50">
+        <v>29.8621235472987</v>
+      </c>
+      <c r="C50">
         <v>28.50418627900196</v>
-      </c>
-      <c r="C50">
-        <v>29.8621235472987</v>
       </c>
       <c r="D50">
         <v>3.508256612596814</v>
       </c>
       <c r="E50">
-        <v>17.99889528919751</v>
+        <v>18.85636129303769</v>
       </c>
       <c r="F50">
         <v>63.1447434177648</v>
       </c>
       <c r="G50">
-        <v>18.85636129303769</v>
+        <v>17.99889528919751</v>
       </c>
     </row>
     <row r="51">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B51">
+        <v>28.60505928177032</v>
+      </c>
+      <c r="C51">
         <v>28.57937764841844</v>
-      </c>
-      <c r="C51">
-        <v>28.60505928177032</v>
       </c>
       <c r="D51">
         <v>3.499026508911188</v>
       </c>
       <c r="E51">
-        <v>18.1820657353702</v>
+        <v>18.19840426980367</v>
       </c>
       <c r="F51">
-        <v>63.61952999482612</v>
+        <v>63.61952999482613</v>
       </c>
       <c r="G51">
-        <v>18.19840426980366</v>
+        <v>18.18206573537021</v>
       </c>
     </row>
     <row r="52">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="B52">
+        <v>31.1973125435761</v>
+      </c>
+      <c r="C52">
         <v>23.02085314064778</v>
-      </c>
-      <c r="C52">
-        <v>31.1973125435761</v>
       </c>
       <c r="D52">
         <v>4.343887665198238</v>
       </c>
       <c r="E52">
-        <v>14.92745879741893</v>
+        <v>20.22933705971806</v>
       </c>
       <c r="F52">
         <v>64.84320414286302</v>
       </c>
       <c r="G52">
-        <v>20.22933705971806</v>
+        <v>14.92745879741893</v>
       </c>
     </row>
     <row r="53">
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B53">
+        <v>28.28196776079512</v>
+      </c>
+      <c r="C53">
         <v>27.46345945043013</v>
-      </c>
-      <c r="C53">
-        <v>28.28196776079512</v>
       </c>
       <c r="D53">
         <v>3.641201873365367</v>
       </c>
       <c r="E53">
+        <v>18.15909992814012</v>
+      </c>
+      <c r="F53">
+        <v>64.20734257859006</v>
+      </c>
+      <c r="G53">
         <v>17.63355749326984</v>
-      </c>
-      <c r="F53">
-        <v>64.20734257859004</v>
-      </c>
-      <c r="G53">
-        <v>18.15909992814012</v>
       </c>
     </row>
   </sheetData>
